--- a/results/04_final_refined_daily_hydroclimate_data/905/Daily_all_temperatures.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/905/Daily_all_temperatures.xlsx
@@ -489,7 +489,7 @@
         <v>28.4</v>
       </c>
       <c r="E2" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="F2" t="n">
         <v>22.1</v>
@@ -508,15 +508,9 @@
       <c r="C3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="F3" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -565,15 +559,9 @@
       <c r="C6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="E6" t="n">
-        <v>17</v>
-      </c>
-      <c r="F6" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -730,15 +718,9 @@
       <c r="C15" t="n">
         <v>14</v>
       </c>
-      <c r="D15" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E15" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="F15" t="n">
-        <v>21.8</v>
-      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -804,15 +786,9 @@
       <c r="C19" t="n">
         <v>18</v>
       </c>
-      <c r="D19" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="E19" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="F19" t="n">
-        <v>20.3</v>
-      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -827,15 +803,9 @@
       <c r="C20" t="n">
         <v>19</v>
       </c>
-      <c r="D20" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="E20" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="F20" t="n">
-        <v>21.8</v>
-      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -867,15 +837,9 @@
       <c r="C22" t="n">
         <v>21</v>
       </c>
-      <c r="D22" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="E22" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="F22" t="n">
-        <v>26.7</v>
-      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -890,15 +854,9 @@
       <c r="C23" t="n">
         <v>22</v>
       </c>
-      <c r="D23" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="E23" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="F23" t="n">
-        <v>21.3</v>
-      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -913,15 +871,9 @@
       <c r="C24" t="n">
         <v>23</v>
       </c>
-      <c r="D24" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="E24" t="n">
-        <v>17</v>
-      </c>
-      <c r="F24" t="n">
-        <v>20.9</v>
-      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
@@ -960,13 +912,13 @@
         <v>25</v>
       </c>
       <c r="D26" t="n">
-        <v>28.1</v>
+        <v>24.7</v>
       </c>
       <c r="E26" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="F26" t="n">
-        <v>22.1</v>
+        <v>20.7</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -982,15 +934,9 @@
       <c r="C27" t="n">
         <v>26</v>
       </c>
-      <c r="D27" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="E27" t="n">
-        <v>16</v>
-      </c>
-      <c r="F27" t="n">
-        <v>20.7</v>
-      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -1006,13 +952,13 @@
         <v>27</v>
       </c>
       <c r="D28" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="E28" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="F28" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -1045,15 +991,9 @@
       <c r="C30" t="n">
         <v>29</v>
       </c>
-      <c r="D30" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E30" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F30" t="n">
-        <v>22.3</v>
-      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -1068,9 +1008,15 @@
       <c r="C31" t="n">
         <v>30</v>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="D31" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="E31" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F31" t="n">
+        <v>22.6</v>
+      </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>

--- a/results/04_final_refined_daily_hydroclimate_data/905/Daily_all_temperatures.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/905/Daily_all_temperatures.xlsx
@@ -489,7 +489,7 @@
         <v>28.4</v>
       </c>
       <c r="E2" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="F2" t="n">
         <v>22.1</v>
@@ -508,9 +508,15 @@
       <c r="C3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="F3" t="n">
+        <v>22.5</v>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -542,9 +548,15 @@
       <c r="C5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>22.2</v>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -576,9 +588,15 @@
       <c r="C7" t="n">
         <v>6</v>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="F7" t="n">
+        <v>21.6</v>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -593,9 +611,15 @@
       <c r="C8" t="n">
         <v>7</v>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="F8" t="n">
+        <v>22.4</v>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -611,13 +635,13 @@
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>26.8</v>
+        <v>27.6</v>
       </c>
       <c r="E9" t="n">
-        <v>17.7</v>
+        <v>17.1</v>
       </c>
       <c r="F9" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -633,7 +657,9 @@
       <c r="C10" t="n">
         <v>9</v>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>24.8</v>
+      </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
@@ -650,9 +676,15 @@
       <c r="C11" t="n">
         <v>10</v>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F11" t="n">
+        <v>22.5</v>
+      </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -684,9 +716,15 @@
       <c r="C13" t="n">
         <v>12</v>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>21.8</v>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -718,9 +756,15 @@
       <c r="C15" t="n">
         <v>14</v>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>28</v>
+      </c>
+      <c r="E15" t="n">
+        <v>17</v>
+      </c>
+      <c r="F15" t="n">
+        <v>22.6</v>
+      </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -735,9 +779,15 @@
       <c r="C16" t="n">
         <v>15</v>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="E16" t="n">
+        <v>17</v>
+      </c>
+      <c r="F16" t="n">
+        <v>22.3</v>
+      </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -752,9 +802,15 @@
       <c r="C17" t="n">
         <v>16</v>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E17" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="F17" t="n">
+        <v>20.3</v>
+      </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -769,9 +825,15 @@
       <c r="C18" t="n">
         <v>17</v>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="F18" t="n">
+        <v>21.8</v>
+      </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -786,9 +848,15 @@
       <c r="C19" t="n">
         <v>18</v>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="E19" t="n">
+        <v>15</v>
+      </c>
+      <c r="F19" t="n">
+        <v>21.9</v>
+      </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -803,9 +871,15 @@
       <c r="C20" t="n">
         <v>19</v>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>21.4</v>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -854,9 +928,15 @@
       <c r="C23" t="n">
         <v>22</v>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+      <c r="D23" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E23" t="n">
+        <v>17</v>
+      </c>
+      <c r="F23" t="n">
+        <v>20.9</v>
+      </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -888,15 +968,9 @@
       <c r="C25" t="n">
         <v>24</v>
       </c>
-      <c r="D25" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="E25" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="F25" t="n">
-        <v>20.7</v>
-      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -911,15 +985,9 @@
       <c r="C26" t="n">
         <v>25</v>
       </c>
-      <c r="D26" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="E26" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="F26" t="n">
-        <v>20.7</v>
-      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -952,13 +1020,13 @@
         <v>27</v>
       </c>
       <c r="D28" t="n">
-        <v>25.4</v>
+        <v>27.5</v>
       </c>
       <c r="E28" t="n">
-        <v>16</v>
+        <v>15.6</v>
       </c>
       <c r="F28" t="n">
-        <v>20.8</v>
+        <v>21.6</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -1008,15 +1076,9 @@
       <c r="C31" t="n">
         <v>30</v>
       </c>
-      <c r="D31" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="E31" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="F31" t="n">
-        <v>22.6</v>
-      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>

--- a/results/04_final_refined_daily_hydroclimate_data/905/Daily_all_temperatures.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/905/Daily_all_temperatures.xlsx
@@ -489,10 +489,10 @@
         <v>28.4</v>
       </c>
       <c r="E2" t="n">
-        <v>15.9</v>
+        <v>15.3</v>
       </c>
       <c r="F2" t="n">
-        <v>22.1</v>
+        <v>22.4</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -508,15 +508,11 @@
       <c r="C3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="n">
-        <v>28.1</v>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="F3" t="n">
-        <v>22.5</v>
-      </c>
+        <v>16.9</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -531,9 +527,15 @@
       <c r="C4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F4" t="n">
+        <v>22.9</v>
+      </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -548,15 +550,11 @@
       <c r="C5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" t="n">
-        <v>28.2</v>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
         <v>16.2</v>
       </c>
-      <c r="F5" t="n">
-        <v>22.2</v>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -571,9 +569,15 @@
       <c r="C6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>17</v>
+      </c>
+      <c r="F6" t="n">
+        <v>22.7</v>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -589,10 +593,10 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>26.6</v>
+        <v>26.4</v>
       </c>
       <c r="E7" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="F7" t="n">
         <v>21.6</v>
@@ -611,15 +615,9 @@
       <c r="C8" t="n">
         <v>7</v>
       </c>
-      <c r="D8" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E8" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="F8" t="n">
-        <v>22.4</v>
-      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -660,8 +658,12 @@
       <c r="D10" t="n">
         <v>24.8</v>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>21.1</v>
+      </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -676,15 +678,9 @@
       <c r="C11" t="n">
         <v>10</v>
       </c>
-      <c r="D11" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="E11" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="F11" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -699,9 +695,15 @@
       <c r="C12" t="n">
         <v>11</v>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>17</v>
+      </c>
+      <c r="F12" t="n">
+        <v>20.9</v>
+      </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -716,15 +718,11 @@
       <c r="C13" t="n">
         <v>12</v>
       </c>
-      <c r="D13" t="n">
-        <v>27.4</v>
-      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
         <v>16.2</v>
       </c>
-      <c r="F13" t="n">
-        <v>21.8</v>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -739,9 +737,15 @@
       <c r="C14" t="n">
         <v>13</v>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E14" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F14" t="n">
+        <v>22.3</v>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -763,7 +767,7 @@
         <v>17</v>
       </c>
       <c r="F15" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -806,10 +810,10 @@
         <v>24.8</v>
       </c>
       <c r="E17" t="n">
-        <v>15.8</v>
+        <v>17.5</v>
       </c>
       <c r="F17" t="n">
-        <v>20.3</v>
+        <v>21</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -826,13 +830,13 @@
         <v>17</v>
       </c>
       <c r="D18" t="n">
-        <v>26.7</v>
+        <v>24.8</v>
       </c>
       <c r="E18" t="n">
-        <v>16.6</v>
+        <v>15.8</v>
       </c>
       <c r="F18" t="n">
-        <v>21.8</v>
+        <v>20.3</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -849,13 +853,13 @@
         <v>18</v>
       </c>
       <c r="D19" t="n">
-        <v>28.8</v>
+        <v>26.8</v>
       </c>
       <c r="E19" t="n">
-        <v>15</v>
+        <v>16.6</v>
       </c>
       <c r="F19" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -872,13 +876,13 @@
         <v>19</v>
       </c>
       <c r="D20" t="n">
-        <v>26.3</v>
+        <v>28.8</v>
       </c>
       <c r="E20" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="F20" t="n">
-        <v>21.4</v>
+        <v>21.9</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -894,9 +898,15 @@
       <c r="C21" t="n">
         <v>20</v>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>21.4</v>
+      </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -911,9 +921,15 @@
       <c r="C22" t="n">
         <v>21</v>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
+      <c r="D22" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E22" t="n">
+        <v>17</v>
+      </c>
+      <c r="F22" t="n">
+        <v>21.7</v>
+      </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -929,13 +945,13 @@
         <v>22</v>
       </c>
       <c r="D23" t="n">
-        <v>24.8</v>
+        <v>27.2</v>
       </c>
       <c r="E23" t="n">
-        <v>17</v>
+        <v>16.1</v>
       </c>
       <c r="F23" t="n">
-        <v>20.9</v>
+        <v>21.8</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -951,9 +967,15 @@
       <c r="C24" t="n">
         <v>23</v>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+      <c r="D24" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E24" t="n">
+        <v>17</v>
+      </c>
+      <c r="F24" t="n">
+        <v>20.9</v>
+      </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
@@ -968,9 +990,15 @@
       <c r="C25" t="n">
         <v>24</v>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+      <c r="D25" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E25" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="F25" t="n">
+        <v>20.7</v>
+      </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -985,9 +1013,15 @@
       <c r="C26" t="n">
         <v>25</v>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="D26" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>22.1</v>
+      </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -1059,9 +1093,15 @@
       <c r="C30" t="n">
         <v>29</v>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="D30" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="E30" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>22.6</v>
+      </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>

--- a/results/04_final_refined_daily_hydroclimate_data/905/Daily_all_temperatures.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/905/Daily_all_temperatures.xlsx
@@ -489,10 +489,10 @@
         <v>28.4</v>
       </c>
       <c r="E2" t="n">
-        <v>15.3</v>
+        <v>15.8</v>
       </c>
       <c r="F2" t="n">
-        <v>22.4</v>
+        <v>22.1</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -550,11 +550,15 @@
       <c r="C5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>28.2</v>
+      </c>
       <c r="E5" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>16.3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>22.1</v>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -592,15 +596,9 @@
       <c r="C7" t="n">
         <v>6</v>
       </c>
-      <c r="D7" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="E7" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="F7" t="n">
-        <v>21.6</v>
-      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -615,9 +613,15 @@
       <c r="C8" t="n">
         <v>7</v>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="F8" t="n">
+        <v>22.4</v>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -633,13 +637,13 @@
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="E9" t="n">
         <v>17.1</v>
       </c>
       <c r="F9" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -678,9 +682,15 @@
       <c r="C11" t="n">
         <v>10</v>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>22.5</v>
+      </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -696,13 +706,13 @@
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>24.8</v>
+        <v>27.7</v>
       </c>
       <c r="E12" t="n">
         <v>17</v>
       </c>
       <c r="F12" t="n">
-        <v>20.9</v>
+        <v>22.4</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -718,11 +728,15 @@
       <c r="C13" t="n">
         <v>12</v>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>27.4</v>
+      </c>
       <c r="E13" t="n">
         <v>16.2</v>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>21.8</v>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -898,15 +912,9 @@
       <c r="C21" t="n">
         <v>20</v>
       </c>
-      <c r="D21" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="E21" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="F21" t="n">
-        <v>21.4</v>
-      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -922,11 +930,9 @@
         <v>21</v>
       </c>
       <c r="D22" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="E22" t="n">
-        <v>17</v>
-      </c>
+        <v>26.3</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
         <v>21.7</v>
       </c>
